--- a/public/calculadora-simples-nacional-configuracoes.xlsx
+++ b/public/calculadora-simples-nacional-configuracoes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thais Camilo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9625C30-4959-4C64-AD68-26A251FC2128}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F616698-BE15-483B-A9DC-18E6A222CD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculadora Simples Nacional" sheetId="1" r:id="rId1"/>

--- a/public/calculadora-simples-nacional-configuracoes.xlsx
+++ b/public/calculadora-simples-nacional-configuracoes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thais Camilo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F616698-BE15-483B-A9DC-18E6A222CD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF070A11-2557-4496-81CC-ABB27080198C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculadora Simples Nacional" sheetId="1" r:id="rId1"/>
@@ -882,7 +882,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>3600000</v>
+        <v>3500000</v>
       </c>
       <c r="D6">
         <v>0.14299999999999999</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="C12">
         <f>C$6</f>
-        <v>3600000</v>
+        <v>3500000</v>
       </c>
       <c r="D12">
         <v>0.14699999999999999</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C18">
         <f>C$6</f>
-        <v>3600000</v>
+        <v>3500000</v>
       </c>
       <c r="D18">
         <v>0.21</v>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C24">
         <f>C$6</f>
-        <v>3600000</v>
+        <v>3500000</v>
       </c>
       <c r="D24">
         <v>0.22</v>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C30">
         <f>C$6</f>
-        <v>3600000</v>
+        <v>3500000</v>
       </c>
       <c r="D30">
         <v>0.23</v>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B3">
         <f>Tabelas_Referencia!C6</f>
-        <v>3600000</v>
+        <v>3500000</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>

--- a/public/calculadora-simples-nacional-configuracoes.xlsx
+++ b/public/calculadora-simples-nacional-configuracoes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thais Camilo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF070A11-2557-4496-81CC-ABB27080198C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F616698-BE15-483B-A9DC-18E6A222CD45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculadora Simples Nacional" sheetId="1" r:id="rId1"/>
@@ -882,7 +882,7 @@
         <v>5</v>
       </c>
       <c r="C6">
-        <v>3500000</v>
+        <v>3600000</v>
       </c>
       <c r="D6">
         <v>0.14299999999999999</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="C12">
         <f>C$6</f>
-        <v>3500000</v>
+        <v>3600000</v>
       </c>
       <c r="D12">
         <v>0.14699999999999999</v>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="C18">
         <f>C$6</f>
-        <v>3500000</v>
+        <v>3600000</v>
       </c>
       <c r="D18">
         <v>0.21</v>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C24">
         <f>C$6</f>
-        <v>3500000</v>
+        <v>3600000</v>
       </c>
       <c r="D24">
         <v>0.22</v>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="C30">
         <f>C$6</f>
-        <v>3500000</v>
+        <v>3600000</v>
       </c>
       <c r="D30">
         <v>0.23</v>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="B3">
         <f>Tabelas_Referencia!C6</f>
-        <v>3500000</v>
+        <v>3600000</v>
       </c>
       <c r="C3" t="s">
         <v>33</v>
